--- a/backend/data/financials_by_company/002167.SZ.xlsx
+++ b/backend/data/financials_by_company/002167.SZ.xlsx
@@ -697,660 +697,660 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-332892.972486</v>
+        <v>-78368.178939</v>
       </c>
       <c r="C2" t="n">
-        <v>0.053233</v>
+        <v>0.060247</v>
       </c>
       <c r="D2" t="n">
-        <v>286572398.71</v>
+        <v>263658788.88</v>
       </c>
       <c r="E2" t="n">
-        <v>-6253508.09</v>
+        <v>-1300772.68</v>
       </c>
       <c r="F2" t="n">
-        <v>-6253508.09</v>
+        <v>-1300772.68</v>
       </c>
       <c r="G2" t="n">
-        <v>176856779.43</v>
+        <v>150510831.72</v>
       </c>
       <c r="H2" t="n">
-        <v>96135077.93000001</v>
+        <v>78897030.84999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1382610213.31</v>
+        <v>974414831.92</v>
       </c>
       <c r="J2" t="n">
-        <v>280318890.62</v>
+        <v>262358016.2</v>
       </c>
       <c r="K2" t="n">
-        <v>184183812.69</v>
+        <v>183460985.35</v>
       </c>
       <c r="L2" t="n">
-        <v>-21089583.37</v>
+        <v>-23802802.6</v>
       </c>
       <c r="M2" t="n">
-        <v>28806252.19</v>
+        <v>23403536.54</v>
       </c>
       <c r="N2" t="n">
-        <v>9964264.08</v>
+        <v>1605202.76</v>
       </c>
       <c r="O2" t="n">
-        <v>182777394.547514</v>
+        <v>151733236.221061</v>
       </c>
       <c r="P2" t="n">
-        <v>176856779.43</v>
+        <v>150510831.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1583830236.43</v>
+        <v>1152626154.5</v>
       </c>
       <c r="R2" t="n">
-        <v>3882705.98</v>
+        <v>1128683.35</v>
       </c>
       <c r="S2" t="n">
-        <v>156056194.54</v>
+        <v>161273378.45</v>
       </c>
       <c r="T2" t="n">
-        <v>768942519</v>
+        <v>716718246</v>
       </c>
       <c r="U2" t="n">
-        <v>768942519</v>
+        <v>716718246</v>
       </c>
       <c r="V2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="W2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="X2" t="n">
-        <v>176856779.43</v>
+        <v>150510831.72</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>176856779.43</v>
+        <v>150510831.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>29750432.02</v>
+        <v>96428.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>147106347.41</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>150414402.81</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="n">
-        <v>147106347.41</v>
+        <v>150414402.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>8271213.09</v>
+        <v>9643046</v>
       </c>
       <c r="AF2" t="n">
-        <v>155377560.5</v>
+        <v>160057448.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>-678634.04</v>
+        <v>-1215929.64</v>
       </c>
       <c r="AH2" t="n">
-        <v>-4886507.9</v>
+        <v>-1300772.68</v>
       </c>
       <c r="AI2" t="n">
-        <v>194095.95</v>
+        <v>-345938.71</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4692411.95</v>
+        <v>1646711.39</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-21089583.37</v>
+        <v>-23802802.6</v>
       </c>
       <c r="AM2" t="n">
-        <v>2247595.26</v>
+        <v>2004468.82</v>
       </c>
       <c r="AN2" t="n">
-        <v>28806252.19</v>
+        <v>23403536.54</v>
       </c>
       <c r="AO2" t="n">
-        <v>9964264.08</v>
+        <v>1605202.76</v>
       </c>
       <c r="AP2" t="n">
-        <v>-40887915.63</v>
+        <v>133677194.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>201220023.12</v>
+        <v>178211322.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>18973663.11</v>
+        <v>12245478.24</v>
       </c>
       <c r="AS2" t="n">
-        <v>32619768.19</v>
+        <v>23870563.98</v>
       </c>
       <c r="AT2" t="n">
-        <v>32619768.19</v>
+        <v>23870563.98</v>
       </c>
       <c r="AU2" t="n">
-        <v>49987854.42</v>
+        <v>56525741.04</v>
       </c>
       <c r="AV2" t="n">
-        <v>51937634.68</v>
+        <v>50022770.53</v>
       </c>
       <c r="AW2" t="n">
-        <v>4156103.19</v>
+        <v>3119423.62</v>
       </c>
       <c r="AX2" t="n">
-        <v>47781531.49</v>
+        <v>46903346.91</v>
       </c>
       <c r="AY2" t="n">
-        <v>3882705.98</v>
+        <v>1128683.35</v>
       </c>
       <c r="AZ2" t="n">
-        <v>160332107.49</v>
+        <v>311888517.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>1382610213.31</v>
+        <v>974414831.92</v>
       </c>
       <c r="BB2" t="n">
-        <v>1542942320.8</v>
+        <v>1286303349.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>1542942320.8</v>
+        <v>1286303349.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-16374279.34</v>
+        <v>-1911815.027141</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.130519</v>
       </c>
       <c r="D3" t="n">
-        <v>85529608.76000001</v>
+        <v>213611774.47</v>
       </c>
       <c r="E3" t="n">
-        <v>-65497117.36</v>
+        <v>-14647766.13</v>
       </c>
       <c r="F3" t="n">
-        <v>-65497117.36</v>
+        <v>-14647766.13</v>
       </c>
       <c r="G3" t="n">
-        <v>-77633193.79000001</v>
+        <v>99059414.75</v>
       </c>
       <c r="H3" t="n">
-        <v>82026641.27</v>
+        <v>74107386.65000001</v>
       </c>
       <c r="I3" t="n">
-        <v>1244284494.1</v>
+        <v>1058153836.78</v>
       </c>
       <c r="J3" t="n">
-        <v>20032491.4</v>
+        <v>198964008.34</v>
       </c>
       <c r="K3" t="n">
-        <v>-61994149.87</v>
+        <v>124856621.69</v>
       </c>
       <c r="L3" t="n">
-        <v>-22225688.84</v>
+        <v>-16029703.07</v>
       </c>
       <c r="M3" t="n">
-        <v>31617097.59</v>
+        <v>17747684.67</v>
       </c>
       <c r="N3" t="n">
-        <v>13324896.29</v>
+        <v>3038106.69</v>
       </c>
       <c r="O3" t="n">
-        <v>-28510355.77</v>
+        <v>111795365.852859</v>
       </c>
       <c r="P3" t="n">
-        <v>-77633193.79000001</v>
+        <v>99059414.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>1470955175.94</v>
+        <v>1258826338.2</v>
       </c>
       <c r="R3" t="n">
-        <v>5352562.42</v>
+        <v>658914.96</v>
       </c>
       <c r="S3" t="n">
-        <v>-93346281.09999999</v>
+        <v>107194267.54</v>
       </c>
       <c r="T3" t="n">
-        <v>776331938</v>
+        <v>707567248</v>
       </c>
       <c r="U3" t="n">
-        <v>776331938</v>
+        <v>707567248</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1</v>
+        <v>0.14</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1</v>
+        <v>0.14</v>
       </c>
       <c r="X3" t="n">
-        <v>-77633193.79000001</v>
+        <v>99059414.75</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-77633193.79000001</v>
+        <v>99059414.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>22338852.17</v>
+        <v>5930252.77</v>
       </c>
       <c r="AB3" t="n">
-        <v>-99972045.95999999</v>
+        <v>93129161.98</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>-99972045.95999999</v>
+        <v>93129161.98</v>
       </c>
       <c r="AE3" t="n">
-        <v>6360798.5</v>
+        <v>13979775.04</v>
       </c>
       <c r="AF3" t="n">
-        <v>-93611247.45999999</v>
+        <v>107108937.02</v>
       </c>
       <c r="AG3" t="n">
-        <v>-264966.36</v>
+        <v>-85330.52</v>
       </c>
       <c r="AH3" t="n">
-        <v>-58294917.91</v>
+        <v>-7416945.77</v>
       </c>
       <c r="AI3" t="n">
-        <v>-300138.84</v>
+        <v>6896.86</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1814817.41</v>
+        <v>1933937.48</v>
       </c>
       <c r="AK3" t="n">
-        <v>56780239.34</v>
+        <v>5476111.43</v>
       </c>
       <c r="AL3" t="n">
-        <v>-22225688.84</v>
+        <v>-16029703.07</v>
       </c>
       <c r="AM3" t="n">
-        <v>3933487.54</v>
+        <v>1320125.09</v>
       </c>
       <c r="AN3" t="n">
-        <v>31617097.59</v>
+        <v>17747684.67</v>
       </c>
       <c r="AO3" t="n">
-        <v>13324896.29</v>
+        <v>3038106.69</v>
       </c>
       <c r="AP3" t="n">
-        <v>-25150678.83</v>
+        <v>110810398.25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>226670681.84</v>
+        <v>200672501.42</v>
       </c>
       <c r="AR3" t="n">
-        <v>12462474.12</v>
+        <v>10294204.82</v>
       </c>
       <c r="AS3" t="n">
-        <v>41345617.28</v>
+        <v>28350143.36</v>
       </c>
       <c r="AT3" t="n">
-        <v>41345617.28</v>
+        <v>28350143.36</v>
       </c>
       <c r="AU3" t="n">
-        <v>74275863.03</v>
+        <v>63235639.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>53683836.08</v>
+        <v>54702458.65</v>
       </c>
       <c r="AW3" t="n">
-        <v>3553568.16</v>
+        <v>2064533.08</v>
       </c>
       <c r="AX3" t="n">
-        <v>50130267.92</v>
+        <v>52637925.57</v>
       </c>
       <c r="AY3" t="n">
-        <v>5352562.42</v>
+        <v>658914.96</v>
       </c>
       <c r="AZ3" t="n">
-        <v>201520003.01</v>
+        <v>311482899.67</v>
       </c>
       <c r="BA3" t="n">
-        <v>1244284494.1</v>
+        <v>1058153836.78</v>
       </c>
       <c r="BB3" t="n">
-        <v>1445804497.11</v>
+        <v>1369636736.45</v>
       </c>
       <c r="BC3" t="n">
-        <v>1445804497.11</v>
+        <v>1369636736.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1911815.027141</v>
+        <v>-16374279.34</v>
       </c>
       <c r="C4" t="n">
-        <v>0.130519</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>213611774.47</v>
+        <v>85529608.76000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-14647766.13</v>
+        <v>-65497117.36</v>
       </c>
       <c r="F4" t="n">
-        <v>-14647766.13</v>
+        <v>-65497117.36</v>
       </c>
       <c r="G4" t="n">
-        <v>99059414.75</v>
+        <v>-77633193.79000001</v>
       </c>
       <c r="H4" t="n">
-        <v>74107386.65000001</v>
+        <v>82026641.27</v>
       </c>
       <c r="I4" t="n">
-        <v>1058153836.78</v>
+        <v>1244284494.1</v>
       </c>
       <c r="J4" t="n">
-        <v>198964008.34</v>
+        <v>20032491.4</v>
       </c>
       <c r="K4" t="n">
-        <v>124856621.69</v>
+        <v>-61994149.87</v>
       </c>
       <c r="L4" t="n">
-        <v>-16029703.07</v>
+        <v>-22225688.84</v>
       </c>
       <c r="M4" t="n">
-        <v>17747684.67</v>
+        <v>31617097.59</v>
       </c>
       <c r="N4" t="n">
-        <v>3038106.69</v>
+        <v>13324896.29</v>
       </c>
       <c r="O4" t="n">
-        <v>111795365.852859</v>
+        <v>-28510355.77</v>
       </c>
       <c r="P4" t="n">
-        <v>99059414.75</v>
+        <v>-77633193.79000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>1258826338.2</v>
+        <v>1470955175.94</v>
       </c>
       <c r="R4" t="n">
-        <v>658914.96</v>
+        <v>5352562.42</v>
       </c>
       <c r="S4" t="n">
-        <v>107194267.54</v>
+        <v>-93346281.09999999</v>
       </c>
       <c r="T4" t="n">
-        <v>707567248</v>
+        <v>776331938</v>
       </c>
       <c r="U4" t="n">
-        <v>707567248</v>
+        <v>776331938</v>
       </c>
       <c r="V4" t="n">
-        <v>0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="X4" t="n">
-        <v>99059414.75</v>
+        <v>-77633193.79000001</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>99059414.75</v>
+        <v>-77633193.79000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>5930252.77</v>
+        <v>22338852.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>93129161.98</v>
+        <v>-99972045.95999999</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>93129161.98</v>
+        <v>-99972045.95999999</v>
       </c>
       <c r="AE4" t="n">
-        <v>13979775.04</v>
+        <v>6360798.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>107108937.02</v>
+        <v>-93611247.45999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>-85330.52</v>
+        <v>-264966.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>-7416945.77</v>
+        <v>-58294917.91</v>
       </c>
       <c r="AI4" t="n">
-        <v>6896.86</v>
+        <v>-300138.84</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1933937.48</v>
+        <v>1814817.41</v>
       </c>
       <c r="AK4" t="n">
-        <v>5476111.43</v>
+        <v>56780239.34</v>
       </c>
       <c r="AL4" t="n">
-        <v>-16029703.07</v>
+        <v>-22225688.84</v>
       </c>
       <c r="AM4" t="n">
-        <v>1320125.09</v>
+        <v>3933487.54</v>
       </c>
       <c r="AN4" t="n">
-        <v>17747684.67</v>
+        <v>31617097.59</v>
       </c>
       <c r="AO4" t="n">
-        <v>3038106.69</v>
+        <v>13324896.29</v>
       </c>
       <c r="AP4" t="n">
-        <v>110810398.25</v>
+        <v>-25150678.83</v>
       </c>
       <c r="AQ4" t="n">
-        <v>200672501.42</v>
+        <v>226670681.84</v>
       </c>
       <c r="AR4" t="n">
-        <v>10294204.82</v>
+        <v>12462474.12</v>
       </c>
       <c r="AS4" t="n">
-        <v>28350143.36</v>
+        <v>41345617.28</v>
       </c>
       <c r="AT4" t="n">
-        <v>28350143.36</v>
+        <v>41345617.28</v>
       </c>
       <c r="AU4" t="n">
-        <v>63235639.4</v>
+        <v>74275863.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>54702458.65</v>
+        <v>53683836.08</v>
       </c>
       <c r="AW4" t="n">
-        <v>2064533.08</v>
+        <v>3553568.16</v>
       </c>
       <c r="AX4" t="n">
-        <v>52637925.57</v>
+        <v>50130267.92</v>
       </c>
       <c r="AY4" t="n">
-        <v>658914.96</v>
+        <v>5352562.42</v>
       </c>
       <c r="AZ4" t="n">
-        <v>311482899.67</v>
+        <v>201520003.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1058153836.78</v>
+        <v>1244284494.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>1369636736.45</v>
+        <v>1445804497.11</v>
       </c>
       <c r="BC4" t="n">
-        <v>1369636736.45</v>
+        <v>1445804497.11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-78368.178939</v>
+        <v>-332892.972486</v>
       </c>
       <c r="C5" t="n">
-        <v>0.060247</v>
+        <v>0.053233</v>
       </c>
       <c r="D5" t="n">
-        <v>263658788.88</v>
+        <v>286572398.71</v>
       </c>
       <c r="E5" t="n">
-        <v>-1300772.68</v>
+        <v>-6253508.09</v>
       </c>
       <c r="F5" t="n">
-        <v>-1300772.68</v>
+        <v>-6253508.09</v>
       </c>
       <c r="G5" t="n">
-        <v>150510831.72</v>
+        <v>176856779.43</v>
       </c>
       <c r="H5" t="n">
-        <v>78897030.84999999</v>
+        <v>96135077.93000001</v>
       </c>
       <c r="I5" t="n">
-        <v>974414831.92</v>
+        <v>1382610213.31</v>
       </c>
       <c r="J5" t="n">
-        <v>262358016.2</v>
+        <v>280318890.62</v>
       </c>
       <c r="K5" t="n">
-        <v>183460985.35</v>
+        <v>184183812.69</v>
       </c>
       <c r="L5" t="n">
-        <v>-23802802.6</v>
+        <v>-21089583.37</v>
       </c>
       <c r="M5" t="n">
-        <v>23403536.54</v>
+        <v>28806252.19</v>
       </c>
       <c r="N5" t="n">
-        <v>1605202.76</v>
+        <v>9964264.08</v>
       </c>
       <c r="O5" t="n">
-        <v>151733236.221061</v>
+        <v>182777394.547514</v>
       </c>
       <c r="P5" t="n">
-        <v>150510831.72</v>
+        <v>176856779.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>1152626154.5</v>
+        <v>1583830236.43</v>
       </c>
       <c r="R5" t="n">
-        <v>1128683.35</v>
+        <v>3882705.98</v>
       </c>
       <c r="S5" t="n">
-        <v>161273378.45</v>
+        <v>156056194.54</v>
       </c>
       <c r="T5" t="n">
-        <v>716718246</v>
+        <v>768942519</v>
       </c>
       <c r="U5" t="n">
-        <v>716718246</v>
+        <v>768942519</v>
       </c>
       <c r="V5" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="X5" t="n">
-        <v>150510831.72</v>
+        <v>176856779.43</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>150510831.72</v>
+        <v>176856779.43</v>
       </c>
       <c r="AA5" t="n">
-        <v>96428.91</v>
+        <v>29750432.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>150414402.81</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
+        <v>147106347.41</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>150414402.81</v>
+        <v>147106347.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>9643046</v>
+        <v>8271213.09</v>
       </c>
       <c r="AF5" t="n">
-        <v>160057448.81</v>
+        <v>155377560.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1215929.64</v>
+        <v>-678634.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1300772.68</v>
+        <v>-4886507.9</v>
       </c>
       <c r="AI5" t="n">
-        <v>-345938.71</v>
+        <v>194095.95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1646711.39</v>
+        <v>4692411.95</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-23802802.6</v>
+        <v>-21089583.37</v>
       </c>
       <c r="AM5" t="n">
-        <v>2004468.82</v>
+        <v>2247595.26</v>
       </c>
       <c r="AN5" t="n">
-        <v>23403536.54</v>
+        <v>28806252.19</v>
       </c>
       <c r="AO5" t="n">
-        <v>1605202.76</v>
+        <v>9964264.08</v>
       </c>
       <c r="AP5" t="n">
-        <v>133677194.75</v>
+        <v>-40887915.63</v>
       </c>
       <c r="AQ5" t="n">
-        <v>178211322.58</v>
+        <v>201220023.12</v>
       </c>
       <c r="AR5" t="n">
-        <v>12245478.24</v>
+        <v>18973663.11</v>
       </c>
       <c r="AS5" t="n">
-        <v>23870563.98</v>
+        <v>32619768.19</v>
       </c>
       <c r="AT5" t="n">
-        <v>23870563.98</v>
+        <v>32619768.19</v>
       </c>
       <c r="AU5" t="n">
-        <v>56525741.04</v>
+        <v>49987854.42</v>
       </c>
       <c r="AV5" t="n">
-        <v>50022770.53</v>
+        <v>51937634.68</v>
       </c>
       <c r="AW5" t="n">
-        <v>3119423.62</v>
+        <v>4156103.19</v>
       </c>
       <c r="AX5" t="n">
-        <v>46903346.91</v>
+        <v>47781531.49</v>
       </c>
       <c r="AY5" t="n">
-        <v>1128683.35</v>
+        <v>3882705.98</v>
       </c>
       <c r="AZ5" t="n">
-        <v>311888517.33</v>
+        <v>160332107.49</v>
       </c>
       <c r="BA5" t="n">
-        <v>974414831.92</v>
+        <v>1382610213.31</v>
       </c>
       <c r="BB5" t="n">
-        <v>1286303349.25</v>
+        <v>1542942320.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>1286303349.25</v>
+        <v>1542942320.8</v>
       </c>
     </row>
   </sheetData>
@@ -1726,850 +1726,850 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>774673300</v>
+        <v>771399000</v>
       </c>
       <c r="C2" t="n">
-        <v>774673300</v>
+        <v>771399000</v>
       </c>
       <c r="D2" t="n">
-        <v>122787461.33</v>
+        <v>190919998.5</v>
       </c>
       <c r="E2" t="n">
-        <v>724829658.99</v>
+        <v>344970218.05</v>
       </c>
       <c r="F2" t="n">
-        <v>1268461332.15</v>
+        <v>789155835.97</v>
       </c>
       <c r="G2" t="n">
-        <v>2369410084.87</v>
+        <v>1597207026.61</v>
       </c>
       <c r="H2" t="n">
-        <v>812766459.4400001</v>
+        <v>-84246779.56</v>
       </c>
       <c r="I2" t="n">
-        <v>1268461332.15</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>789155835.97</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12092550.68</v>
+      </c>
       <c r="K2" t="n">
-        <v>1708843948.82</v>
+        <v>1269207026.61</v>
       </c>
       <c r="L2" t="n">
-        <v>1956543948.82</v>
+        <v>1329207026.61</v>
       </c>
       <c r="M2" t="n">
-        <v>1708843948.82</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>1221177565.37</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-48029461.24</v>
+      </c>
       <c r="O2" t="n">
-        <v>1708843948.82</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>1269207026.61</v>
+      </c>
+      <c r="P2" t="n">
+        <v>191607350</v>
+      </c>
       <c r="Q2" t="n">
-        <v>-148936107.03</v>
+        <v>-347235007.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1119587117.11</v>
+        <v>1045399708.11</v>
       </c>
       <c r="S2" t="n">
-        <v>774673300</v>
+        <v>771341000</v>
       </c>
       <c r="T2" t="n">
-        <v>774673300</v>
+        <v>771341000</v>
       </c>
       <c r="U2" t="n">
-        <v>1016079500.81</v>
+        <v>890562224.4299999</v>
       </c>
       <c r="V2" t="n">
-        <v>258730348.54</v>
+        <v>83296606.40000001</v>
       </c>
       <c r="W2" t="n">
-        <v>7913332.72</v>
+        <v>8217332.92</v>
       </c>
       <c r="X2" t="n">
-        <v>3117015.82</v>
+        <v>2986722.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>247700000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>72092550.68000001</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12092550.68</v>
+      </c>
       <c r="AA2" t="n">
-        <v>247700000</v>
+        <v>60000000</v>
       </c>
       <c r="AB2" t="n">
-        <v>757349152.27</v>
+        <v>807265618.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>3269355.49</v>
+        <v>4618295.31</v>
       </c>
       <c r="AD2" t="n">
-        <v>477129658.99</v>
+        <v>272877667.37</v>
       </c>
       <c r="AE2" t="n">
-        <v>412866136.05</v>
+        <v>268000000</v>
       </c>
       <c r="AF2" t="n">
-        <v>270862910.72</v>
+        <v>487697278.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>38364391.1</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>226967507.29</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
       <c r="AI2" t="n">
-        <v>8196183.11</v>
+        <v>15582280.17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>224302336.51</v>
+        <v>245147491.49</v>
       </c>
       <c r="AK2" t="n">
-        <v>2724923449.63</v>
+        <v>2111739789.8</v>
       </c>
       <c r="AL2" t="n">
-        <v>1154807837.92</v>
+        <v>1388720951.33</v>
       </c>
       <c r="AM2" t="n">
-        <v>2817536.92</v>
+        <v>5617298.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>2494150.85</v>
+        <v>1682040.45</v>
       </c>
       <c r="AO2" t="n">
-        <v>288121.26</v>
+        <v>579410.0600000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>23121635.18</v>
+        <v>305052</v>
       </c>
       <c r="AQ2" t="n">
-        <v>23121635.18</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>305052</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>128490741.79</v>
+      </c>
       <c r="AS2" t="n">
-        <v>440382616.67</v>
+        <v>480051190.64</v>
       </c>
       <c r="AT2" t="n">
-        <v>417407420.68</v>
+        <v>457075994.65</v>
       </c>
       <c r="AU2" t="n">
         <v>22975195.99</v>
       </c>
       <c r="AV2" t="n">
-        <v>685703777.04</v>
+        <v>770153949.79</v>
       </c>
       <c r="AW2" t="n">
-        <v>-739382785.4</v>
+        <v>-843252328.61</v>
       </c>
       <c r="AX2" t="n">
-        <v>1425086562.44</v>
+        <v>1613406278.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>7881073.58</v>
+        <v>43903166.25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13725675.36</v>
+        <v>30254146.43</v>
       </c>
       <c r="BA2" t="n">
-        <v>688259332.35</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
+        <v>770999861.09</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>618233677.09</v>
+      </c>
       <c r="BC2" t="n">
-        <v>715220481.15</v>
+        <v>768249104.63</v>
       </c>
       <c r="BD2" t="n">
-        <v>1570115611.71</v>
+        <v>723018838.47</v>
       </c>
       <c r="BE2" t="n">
-        <v>32956750.43</v>
+        <v>25830412.91</v>
       </c>
       <c r="BF2" t="n">
-        <v>200336269.23</v>
+        <v>31113844.39</v>
       </c>
       <c r="BG2" t="n">
-        <v>631861025.79</v>
+        <v>420196014.18</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
-      <c r="BI2" t="inlineStr"/>
+      <c r="BI2" t="n">
+        <v>1074875.3</v>
+      </c>
       <c r="BJ2" t="n">
-        <v>379485818.66</v>
+        <v>230442969.11</v>
       </c>
       <c r="BK2" t="n">
-        <v>139580293.81</v>
+        <v>137167149.66</v>
       </c>
       <c r="BL2" t="n">
-        <v>112794913.32</v>
+        <v>51511020.11</v>
       </c>
       <c r="BM2" t="n">
-        <v>13721768.28</v>
+        <v>10523531.22</v>
       </c>
       <c r="BN2" t="n">
-        <v>153461123.26</v>
+        <v>98275034.27</v>
       </c>
       <c r="BO2" t="n">
-        <v>-23044447.33</v>
+        <v>-37047503.91</v>
       </c>
       <c r="BP2" t="n">
-        <v>176505570.59</v>
+        <v>135322538.18</v>
       </c>
       <c r="BQ2" t="n">
-        <v>537778674.72</v>
+        <v>137080001.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>537778674.72</v>
+        <v>137080001.5</v>
       </c>
       <c r="BS2" t="n">
-        <v>220118292.22</v>
+        <v>90415030.12</v>
       </c>
       <c r="BT2" t="n">
-        <v>317660382.5</v>
+        <v>46664971.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>774902500</v>
+        <v>775134000</v>
       </c>
       <c r="C3" t="n">
-        <v>774902500</v>
-      </c>
-      <c r="D3" t="n">
-        <v>257607365.56</v>
-      </c>
+        <v>775134000</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>840757745.9</v>
+        <v>621274321.03</v>
       </c>
       <c r="F3" t="n">
-        <v>945406816.02</v>
+        <v>925774945</v>
       </c>
       <c r="G3" t="n">
-        <v>2253273500.93</v>
+        <v>2003784910.9</v>
       </c>
       <c r="H3" t="n">
-        <v>-538597225.6</v>
+        <v>-263225763.49</v>
       </c>
       <c r="I3" t="n">
-        <v>945406816.02</v>
+        <v>925774945</v>
       </c>
       <c r="J3" t="n">
-        <v>1216569.68</v>
+        <v>8875881.539999999</v>
       </c>
       <c r="K3" t="n">
-        <v>1448153213.93</v>
+        <v>1450894910.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1565653213.93</v>
+        <v>1480494910.9</v>
       </c>
       <c r="M3" t="n">
-        <v>1370661352.57</v>
+        <v>1396787317.79</v>
       </c>
       <c r="N3" t="n">
-        <v>-77491861.36</v>
+        <v>-54107593.11</v>
       </c>
       <c r="O3" t="n">
-        <v>1448153213.93</v>
+        <v>1450894910.9</v>
       </c>
       <c r="P3" t="n">
-        <v>84126120</v>
+        <v>149904025</v>
       </c>
       <c r="Q3" t="n">
-        <v>-325792886.46</v>
+        <v>-248159692.67</v>
       </c>
       <c r="R3" t="n">
-        <v>1098951113.11</v>
+        <v>1079081888.11</v>
       </c>
       <c r="S3" t="n">
-        <v>774902500</v>
+        <v>775134000</v>
       </c>
       <c r="T3" t="n">
-        <v>774902500</v>
+        <v>775134000</v>
       </c>
       <c r="U3" t="n">
-        <v>2053598185.3</v>
+        <v>1734952876.72</v>
       </c>
       <c r="V3" t="n">
-        <v>130955100.71</v>
+        <v>51267536.82</v>
       </c>
       <c r="W3" t="n">
-        <v>8300318.28</v>
+        <v>8059912.56</v>
       </c>
       <c r="X3" t="n">
-        <v>3938212.75</v>
+        <v>4731742.72</v>
       </c>
       <c r="Y3" t="n">
-        <v>118716569.68</v>
+        <v>38475881.54</v>
       </c>
       <c r="Z3" t="n">
-        <v>1216569.68</v>
+        <v>8875881.539999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>117500000</v>
+        <v>29600000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1922643084.59</v>
+        <v>1683685339.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>34776664.38</v>
+        <v>26226179.34</v>
       </c>
       <c r="AD3" t="n">
-        <v>722041176.22</v>
+        <v>582798439.49</v>
       </c>
       <c r="AE3" t="n">
-        <v>687620287</v>
+        <v>523290000</v>
       </c>
       <c r="AF3" t="n">
-        <v>824459312.83</v>
+        <v>822095730.49</v>
       </c>
       <c r="AG3" t="n">
-        <v>118102373.21</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>179223656.85</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
       <c r="AI3" t="n">
-        <v>10306741.22</v>
+        <v>31813594.76</v>
       </c>
       <c r="AJ3" t="n">
-        <v>696050198.4</v>
+        <v>611058478.88</v>
       </c>
       <c r="AK3" t="n">
-        <v>3424259537.87</v>
+        <v>3131740194.51</v>
       </c>
       <c r="AL3" t="n">
-        <v>2040213678.88</v>
+        <v>1711280618.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>98704430</v>
+        <v>2059930</v>
       </c>
       <c r="AN3" t="n">
-        <v>700126.54</v>
+        <v>977777.85</v>
       </c>
       <c r="AO3" t="n">
-        <v>1083407.14</v>
+        <v>3370269.87</v>
       </c>
       <c r="AP3" t="n">
-        <v>319994.4</v>
+        <v>311110.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>319994.4</v>
+        <v>311110.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>144072077.14</v>
+        <v>145291393.47</v>
       </c>
       <c r="AS3" t="n">
-        <v>502746397.91</v>
+        <v>525119965.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>479771201.92</v>
+        <v>502144769.91</v>
       </c>
       <c r="AU3" t="n">
         <v>22975195.99</v>
       </c>
       <c r="AV3" t="n">
-        <v>1292517815.63</v>
+        <v>1032262781.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>-955187508.54</v>
+        <v>-897925559.3200001</v>
       </c>
       <c r="AX3" t="n">
-        <v>2247705324.17</v>
+        <v>1930188340.52</v>
       </c>
       <c r="AY3" t="n">
-        <v>574973067.54</v>
+        <v>349674003.56</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19455731.05</v>
+        <v>29872373.92</v>
       </c>
       <c r="BA3" t="n">
-        <v>827906776.17</v>
+        <v>777305002.33</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>825369749.41</v>
+        <v>773336960.71</v>
       </c>
       <c r="BD3" t="n">
-        <v>1384045858.99</v>
+        <v>1420459576.41</v>
       </c>
       <c r="BE3" t="n">
-        <v>38733243.06</v>
+        <v>28159827.62</v>
       </c>
       <c r="BF3" t="n">
-        <v>28894667.95</v>
+        <v>71683891.63</v>
       </c>
       <c r="BG3" t="n">
-        <v>531278230.43</v>
+        <v>529834759.64</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>1251523.75</v>
+        <v>431396.47</v>
       </c>
       <c r="BJ3" t="n">
-        <v>246984276.56</v>
+        <v>257515992</v>
       </c>
       <c r="BK3" t="n">
-        <v>161931007.28</v>
+        <v>168738666.89</v>
       </c>
       <c r="BL3" t="n">
-        <v>121111422.84</v>
+        <v>103148704.28</v>
       </c>
       <c r="BM3" t="n">
-        <v>52103963.05</v>
+        <v>41765572.05</v>
       </c>
       <c r="BN3" t="n">
-        <v>185522833.06</v>
+        <v>142259976.81</v>
       </c>
       <c r="BO3" t="n">
-        <v>-19332306.92</v>
+        <v>-21752354.83</v>
       </c>
       <c r="BP3" t="n">
-        <v>204855139.98</v>
+        <v>164012331.64</v>
       </c>
       <c r="BQ3" t="n">
-        <v>547512921.4400001</v>
+        <v>606755548.66</v>
       </c>
       <c r="BR3" t="n">
-        <v>547512921.4400001</v>
+        <v>606755548.66</v>
       </c>
       <c r="BS3" t="n">
-        <v>461126289.05</v>
+        <v>523988064.42</v>
       </c>
       <c r="BT3" t="n">
-        <v>86386632.39</v>
+        <v>82767484.23999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>775134000</v>
+        <v>774902500</v>
       </c>
       <c r="C4" t="n">
-        <v>775134000</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>774902500</v>
+      </c>
+      <c r="D4" t="n">
+        <v>257607365.56</v>
+      </c>
       <c r="E4" t="n">
-        <v>621274321.03</v>
+        <v>840757745.9</v>
       </c>
       <c r="F4" t="n">
-        <v>925774945</v>
+        <v>945406816.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2003784910.9</v>
+        <v>2253273500.93</v>
       </c>
       <c r="H4" t="n">
-        <v>-263225763.49</v>
+        <v>-538597225.6</v>
       </c>
       <c r="I4" t="n">
-        <v>925774945</v>
+        <v>945406816.02</v>
       </c>
       <c r="J4" t="n">
-        <v>8875881.539999999</v>
+        <v>1216569.68</v>
       </c>
       <c r="K4" t="n">
-        <v>1450894910.9</v>
+        <v>1448153213.93</v>
       </c>
       <c r="L4" t="n">
-        <v>1480494910.9</v>
+        <v>1565653213.93</v>
       </c>
       <c r="M4" t="n">
-        <v>1396787317.79</v>
+        <v>1370661352.57</v>
       </c>
       <c r="N4" t="n">
-        <v>-54107593.11</v>
+        <v>-77491861.36</v>
       </c>
       <c r="O4" t="n">
-        <v>1450894910.9</v>
+        <v>1448153213.93</v>
       </c>
       <c r="P4" t="n">
-        <v>149904025</v>
+        <v>84126120</v>
       </c>
       <c r="Q4" t="n">
-        <v>-248159692.67</v>
+        <v>-325792886.46</v>
       </c>
       <c r="R4" t="n">
-        <v>1079081888.11</v>
+        <v>1098951113.11</v>
       </c>
       <c r="S4" t="n">
-        <v>775134000</v>
+        <v>774902500</v>
       </c>
       <c r="T4" t="n">
-        <v>775134000</v>
+        <v>774902500</v>
       </c>
       <c r="U4" t="n">
-        <v>1734952876.72</v>
+        <v>2053598185.3</v>
       </c>
       <c r="V4" t="n">
-        <v>51267536.82</v>
+        <v>130955100.71</v>
       </c>
       <c r="W4" t="n">
-        <v>8059912.56</v>
+        <v>8300318.28</v>
       </c>
       <c r="X4" t="n">
-        <v>4731742.72</v>
+        <v>3938212.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>38475881.54</v>
+        <v>118716569.68</v>
       </c>
       <c r="Z4" t="n">
-        <v>8875881.539999999</v>
+        <v>1216569.68</v>
       </c>
       <c r="AA4" t="n">
-        <v>29600000</v>
+        <v>117500000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1683685339.9</v>
+        <v>1922643084.59</v>
       </c>
       <c r="AC4" t="n">
-        <v>26226179.34</v>
+        <v>34776664.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>582798439.49</v>
+        <v>722041176.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>523290000</v>
+        <v>687620287</v>
       </c>
       <c r="AF4" t="n">
-        <v>822095730.49</v>
+        <v>824459312.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>179223656.85</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
+        <v>118102373.21</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>31813594.76</v>
+        <v>10306741.22</v>
       </c>
       <c r="AJ4" t="n">
-        <v>611058478.88</v>
+        <v>696050198.4</v>
       </c>
       <c r="AK4" t="n">
-        <v>3131740194.51</v>
+        <v>3424259537.87</v>
       </c>
       <c r="AL4" t="n">
-        <v>1711280618.1</v>
+        <v>2040213678.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>2059930</v>
+        <v>98704430</v>
       </c>
       <c r="AN4" t="n">
-        <v>977777.85</v>
+        <v>700126.54</v>
       </c>
       <c r="AO4" t="n">
-        <v>3370269.87</v>
+        <v>1083407.14</v>
       </c>
       <c r="AP4" t="n">
-        <v>311110.8</v>
+        <v>319994.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>311110.8</v>
+        <v>319994.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>145291393.47</v>
+        <v>144072077.14</v>
       </c>
       <c r="AS4" t="n">
-        <v>525119965.9</v>
+        <v>502746397.91</v>
       </c>
       <c r="AT4" t="n">
-        <v>502144769.91</v>
+        <v>479771201.92</v>
       </c>
       <c r="AU4" t="n">
         <v>22975195.99</v>
       </c>
       <c r="AV4" t="n">
-        <v>1032262781.2</v>
+        <v>1292517815.63</v>
       </c>
       <c r="AW4" t="n">
-        <v>-897925559.3200001</v>
+        <v>-955187508.54</v>
       </c>
       <c r="AX4" t="n">
-        <v>1930188340.52</v>
+        <v>2247705324.17</v>
       </c>
       <c r="AY4" t="n">
-        <v>349674003.56</v>
+        <v>574973067.54</v>
       </c>
       <c r="AZ4" t="n">
-        <v>29872373.92</v>
+        <v>19455731.05</v>
       </c>
       <c r="BA4" t="n">
-        <v>777305002.33</v>
+        <v>827906776.17</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>773336960.71</v>
+        <v>825369749.41</v>
       </c>
       <c r="BD4" t="n">
-        <v>1420459576.41</v>
+        <v>1384045858.99</v>
       </c>
       <c r="BE4" t="n">
-        <v>28159827.62</v>
+        <v>38733243.06</v>
       </c>
       <c r="BF4" t="n">
-        <v>71683891.63</v>
+        <v>28894667.95</v>
       </c>
       <c r="BG4" t="n">
-        <v>529834759.64</v>
+        <v>531278230.43</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>431396.47</v>
+        <v>1251523.75</v>
       </c>
       <c r="BJ4" t="n">
-        <v>257515992</v>
+        <v>246984276.56</v>
       </c>
       <c r="BK4" t="n">
-        <v>168738666.89</v>
+        <v>161931007.28</v>
       </c>
       <c r="BL4" t="n">
-        <v>103148704.28</v>
+        <v>121111422.84</v>
       </c>
       <c r="BM4" t="n">
-        <v>41765572.05</v>
+        <v>52103963.05</v>
       </c>
       <c r="BN4" t="n">
-        <v>142259976.81</v>
+        <v>185522833.06</v>
       </c>
       <c r="BO4" t="n">
-        <v>-21752354.83</v>
+        <v>-19332306.92</v>
       </c>
       <c r="BP4" t="n">
-        <v>164012331.64</v>
+        <v>204855139.98</v>
       </c>
       <c r="BQ4" t="n">
-        <v>606755548.66</v>
+        <v>547512921.4400001</v>
       </c>
       <c r="BR4" t="n">
-        <v>606755548.66</v>
+        <v>547512921.4400001</v>
       </c>
       <c r="BS4" t="n">
-        <v>523988064.42</v>
+        <v>461126289.05</v>
       </c>
       <c r="BT4" t="n">
-        <v>82767484.23999999</v>
+        <v>86386632.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>771399000</v>
+        <v>774673300</v>
       </c>
       <c r="C5" t="n">
-        <v>771399000</v>
+        <v>774673300</v>
       </c>
       <c r="D5" t="n">
-        <v>190919998.5</v>
+        <v>122787461.33</v>
       </c>
       <c r="E5" t="n">
-        <v>344970218.05</v>
+        <v>724829658.99</v>
       </c>
       <c r="F5" t="n">
-        <v>789155835.97</v>
+        <v>1268461332.15</v>
       </c>
       <c r="G5" t="n">
-        <v>1597207026.61</v>
+        <v>2369410084.87</v>
       </c>
       <c r="H5" t="n">
-        <v>-84246779.56</v>
+        <v>812766459.4400001</v>
       </c>
       <c r="I5" t="n">
-        <v>789155835.97</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12092550.68</v>
-      </c>
+        <v>1268461332.15</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>1269207026.61</v>
+        <v>1708843948.82</v>
       </c>
       <c r="L5" t="n">
-        <v>1329207026.61</v>
+        <v>1956543948.82</v>
       </c>
       <c r="M5" t="n">
-        <v>1221177565.37</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-48029461.24</v>
-      </c>
+        <v>1708843948.82</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>1269207026.61</v>
-      </c>
-      <c r="P5" t="n">
-        <v>191607350</v>
-      </c>
+        <v>1708843948.82</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>-347235007.4</v>
+        <v>-148936107.03</v>
       </c>
       <c r="R5" t="n">
-        <v>1045399708.11</v>
+        <v>1119587117.11</v>
       </c>
       <c r="S5" t="n">
-        <v>771341000</v>
+        <v>774673300</v>
       </c>
       <c r="T5" t="n">
-        <v>771341000</v>
+        <v>774673300</v>
       </c>
       <c r="U5" t="n">
-        <v>890562224.4299999</v>
+        <v>1016079500.81</v>
       </c>
       <c r="V5" t="n">
-        <v>83296606.40000001</v>
+        <v>258730348.54</v>
       </c>
       <c r="W5" t="n">
-        <v>8217332.92</v>
+        <v>7913332.72</v>
       </c>
       <c r="X5" t="n">
-        <v>2986722.8</v>
+        <v>3117015.82</v>
       </c>
       <c r="Y5" t="n">
-        <v>72092550.68000001</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>12092550.68</v>
-      </c>
+        <v>247700000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>60000000</v>
+        <v>247700000</v>
       </c>
       <c r="AB5" t="n">
-        <v>807265618.03</v>
+        <v>757349152.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>4618295.31</v>
+        <v>3269355.49</v>
       </c>
       <c r="AD5" t="n">
-        <v>272877667.37</v>
+        <v>477129658.99</v>
       </c>
       <c r="AE5" t="n">
-        <v>268000000</v>
+        <v>412866136.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>487697278.95</v>
+        <v>270862910.72</v>
       </c>
       <c r="AG5" t="n">
-        <v>226967507.29</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
+        <v>38364391.1</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>15582280.17</v>
+        <v>8196183.11</v>
       </c>
       <c r="AJ5" t="n">
-        <v>245147491.49</v>
+        <v>224302336.51</v>
       </c>
       <c r="AK5" t="n">
-        <v>2111739789.8</v>
+        <v>2724923449.63</v>
       </c>
       <c r="AL5" t="n">
-        <v>1388720951.33</v>
+        <v>1154807837.92</v>
       </c>
       <c r="AM5" t="n">
-        <v>5617298.5</v>
+        <v>2817536.92</v>
       </c>
       <c r="AN5" t="n">
-        <v>1682040.45</v>
+        <v>2494150.85</v>
       </c>
       <c r="AO5" t="n">
-        <v>579410.0600000001</v>
+        <v>288121.26</v>
       </c>
       <c r="AP5" t="n">
-        <v>305052</v>
+        <v>23121635.18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>305052</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>128490741.79</v>
-      </c>
+        <v>23121635.18</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>480051190.64</v>
+        <v>440382616.67</v>
       </c>
       <c r="AT5" t="n">
-        <v>457075994.65</v>
+        <v>417407420.68</v>
       </c>
       <c r="AU5" t="n">
         <v>22975195.99</v>
       </c>
       <c r="AV5" t="n">
-        <v>770153949.79</v>
+        <v>685703777.04</v>
       </c>
       <c r="AW5" t="n">
-        <v>-843252328.61</v>
+        <v>-739382785.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>1613406278.4</v>
+        <v>1425086562.44</v>
       </c>
       <c r="AY5" t="n">
-        <v>43903166.25</v>
+        <v>7881073.58</v>
       </c>
       <c r="AZ5" t="n">
-        <v>30254146.43</v>
+        <v>13725675.36</v>
       </c>
       <c r="BA5" t="n">
-        <v>770999861.09</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>618233677.09</v>
-      </c>
+        <v>688259332.35</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>768249104.63</v>
+        <v>715220481.15</v>
       </c>
       <c r="BD5" t="n">
-        <v>723018838.47</v>
+        <v>1570115611.71</v>
       </c>
       <c r="BE5" t="n">
-        <v>25830412.91</v>
+        <v>32956750.43</v>
       </c>
       <c r="BF5" t="n">
-        <v>31113844.39</v>
+        <v>200336269.23</v>
       </c>
       <c r="BG5" t="n">
-        <v>420196014.18</v>
+        <v>631861025.79</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
-      <c r="BI5" t="n">
-        <v>1074875.3</v>
-      </c>
+      <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="n">
-        <v>230442969.11</v>
+        <v>379485818.66</v>
       </c>
       <c r="BK5" t="n">
-        <v>137167149.66</v>
+        <v>139580293.81</v>
       </c>
       <c r="BL5" t="n">
-        <v>51511020.11</v>
+        <v>112794913.32</v>
       </c>
       <c r="BM5" t="n">
-        <v>10523531.22</v>
+        <v>13721768.28</v>
       </c>
       <c r="BN5" t="n">
-        <v>98275034.27</v>
+        <v>153461123.26</v>
       </c>
       <c r="BO5" t="n">
-        <v>-37047503.91</v>
+        <v>-23044447.33</v>
       </c>
       <c r="BP5" t="n">
-        <v>135322538.18</v>
+        <v>176505570.59</v>
       </c>
       <c r="BQ5" t="n">
-        <v>137080001.5</v>
+        <v>537778674.72</v>
       </c>
       <c r="BR5" t="n">
-        <v>137080001.5</v>
+        <v>537778674.72</v>
       </c>
       <c r="BS5" t="n">
-        <v>90415030.12</v>
+        <v>220118292.22</v>
       </c>
       <c r="BT5" t="n">
-        <v>46664971.38</v>
+        <v>317660382.5</v>
       </c>
     </row>
   </sheetData>
@@ -2830,570 +2830,570 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>641226060.6900001</v>
+        <v>154209742.61</v>
       </c>
       <c r="C2" t="n">
-        <v>-822120287</v>
+        <v>-1063500000</v>
       </c>
       <c r="D2" t="n">
-        <v>562863380</v>
+        <v>688700000</v>
       </c>
       <c r="E2" t="n">
-        <v>-77031590.34999999</v>
+        <v>-41878422.92</v>
       </c>
       <c r="F2" t="n">
-        <v>317660382.5</v>
+        <v>46664971.38</v>
       </c>
       <c r="G2" t="n">
-        <v>86386632.39</v>
+        <v>15726821.66</v>
       </c>
       <c r="H2" t="n">
-        <v>-16463297.78</v>
+        <v>-1238357.62</v>
       </c>
       <c r="I2" t="n">
-        <v>247737047.89</v>
+        <v>32176507.34</v>
       </c>
       <c r="J2" t="n">
-        <v>-327557100.29</v>
+        <v>-205532468.87</v>
       </c>
       <c r="K2" t="n">
-        <v>-45977060.23</v>
+        <v>206848312.56</v>
       </c>
       <c r="L2" t="n">
-        <v>-22323133.06</v>
+        <v>-37580781.43</v>
       </c>
       <c r="M2" t="n">
-        <v>-259256907</v>
+        <v>-374800000</v>
       </c>
       <c r="N2" t="n">
-        <v>-259256907</v>
+        <v>-374800000</v>
       </c>
       <c r="O2" t="n">
-        <v>-822120287</v>
+        <v>-1063500000</v>
       </c>
       <c r="P2" t="n">
-        <v>562863380</v>
+        <v>688700000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-142963502.86</v>
+        <v>41620810.68</v>
       </c>
       <c r="R2" t="n">
-        <v>-114375086.02</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+        <v>-41878422.92</v>
+      </c>
+      <c r="S2" t="n">
+        <v>19684120.86</v>
+      </c>
+      <c r="T2" t="n">
+        <v>19684120.86</v>
+      </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>47574487.21</v>
+        <v>63610580.74</v>
       </c>
       <c r="W2" t="n">
-        <v>47574487.21</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
+        <v>163589450.19</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-99978869.45</v>
+      </c>
       <c r="Y2" t="n">
-        <v>-76162904.05</v>
+        <v>-41673890.92</v>
       </c>
       <c r="Z2" t="n">
-        <v>868686.3</v>
+        <v>204532</v>
       </c>
       <c r="AA2" t="n">
-        <v>-77031590.34999999</v>
+        <v>-41878422.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>718257651.04</v>
+        <v>196088165.53</v>
       </c>
       <c r="AC2" t="n">
-        <v>717626647.8200001</v>
+        <v>-37883747.65</v>
       </c>
       <c r="AD2" t="n">
-        <v>-25911.05</v>
+        <v>2433393.19</v>
       </c>
       <c r="AE2" t="n">
-        <v>1372153016.85</v>
+        <v>-47233725.54</v>
       </c>
       <c r="AF2" t="n">
-        <v>-205052323.32</v>
+        <v>-81655766.59999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>-449448134.66</v>
+        <v>88572351.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>26979042.49</v>
+        <v>26912309.32</v>
       </c>
       <c r="AI2" t="n">
-        <v>96135077.93000001</v>
+        <v>78897030.84999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25263435.84</v>
+        <v>13024098.24</v>
       </c>
       <c r="AK2" t="n">
-        <v>70871642.09</v>
+        <v>65872932.61</v>
       </c>
       <c r="AL2" t="n">
-        <v>-275560716.9</v>
+        <v>-55763281.11</v>
       </c>
       <c r="AM2" t="n">
-        <v>755440.42</v>
+        <v>-249860.08</v>
       </c>
       <c r="AN2" t="n">
-        <v>147106347.41</v>
+        <v>150414402.81</v>
       </c>
       <c r="AO2" t="n">
-        <v>718257651.04</v>
+        <v>196088165.53</v>
       </c>
       <c r="AP2" t="n">
-        <v>-48375280.36</v>
+        <v>-53287273.97</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-726616683.37</v>
+        <v>-821986198.3099999</v>
       </c>
       <c r="AR2" t="n">
-        <v>-191509100.43</v>
+        <v>-102160445.75</v>
       </c>
       <c r="AS2" t="n">
-        <v>-168741766.27</v>
+        <v>-107244792.38</v>
       </c>
       <c r="AT2" t="n">
-        <v>-366365816.67</v>
+        <v>-612580960.1799999</v>
       </c>
       <c r="AU2" t="n">
-        <v>1493249614.77</v>
+        <v>1071361637.81</v>
       </c>
       <c r="AV2" t="n">
-        <v>149997154.96</v>
+        <v>104195013.18</v>
       </c>
       <c r="AW2" t="n">
-        <v>1343252459.81</v>
+        <v>967166624.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-252770688.25</v>
+        <v>-288128494.23</v>
       </c>
       <c r="C3" t="n">
-        <v>-691190000</v>
+        <v>-364000000</v>
       </c>
       <c r="D3" t="n">
-        <v>922311050.89</v>
+        <v>643290000</v>
       </c>
       <c r="E3" t="n">
-        <v>-321581797.13</v>
+        <v>-332081469.88</v>
       </c>
       <c r="F3" t="n">
-        <v>86386632.39</v>
+        <v>82767484.23999999</v>
       </c>
       <c r="G3" t="n">
-        <v>82767484.23999999</v>
+        <v>46664971.38</v>
       </c>
       <c r="H3" t="n">
-        <v>-1124576.23</v>
+        <v>7405686.02</v>
       </c>
       <c r="I3" t="n">
-        <v>4743724.38</v>
+        <v>28696826.84</v>
       </c>
       <c r="J3" t="n">
-        <v>256883711.93</v>
+        <v>311849952.66</v>
       </c>
       <c r="K3" t="n">
-        <v>62419264.24</v>
+        <v>51389981.98</v>
       </c>
       <c r="L3" t="n">
-        <v>-36656603.2</v>
+        <v>-18830029.32</v>
       </c>
       <c r="M3" t="n">
-        <v>231121050.89</v>
+        <v>279290000</v>
       </c>
       <c r="N3" t="n">
-        <v>231121050.89</v>
+        <v>279290000</v>
       </c>
       <c r="O3" t="n">
-        <v>-691190000</v>
+        <v>-364000000</v>
       </c>
       <c r="P3" t="n">
-        <v>922311050.89</v>
+        <v>643290000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-320951096.43</v>
+        <v>-327106101.47</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+        <v>4800528.41</v>
+      </c>
+      <c r="T3" t="n">
+        <v>37531656.3</v>
+      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-32731127.89</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-320951096.43</v>
+        <v>-331906629.88</v>
       </c>
       <c r="Z3" t="n">
-        <v>630700.7</v>
+        <v>174840</v>
       </c>
       <c r="AA3" t="n">
-        <v>-321581797.13</v>
+        <v>-332081469.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>68811108.88</v>
+        <v>43952975.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>-21097165.89</v>
+        <v>-151505575.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>1494950.03</v>
+        <v>-1029635.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>1215391872.13</v>
+        <v>287508151.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>-57629203.72</v>
+        <v>-115046910.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1180354784.33</v>
+        <v>-322937181.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>32787213.36</v>
+        <v>10967526.31</v>
       </c>
       <c r="AI3" t="n">
-        <v>82026641.27</v>
+        <v>74107386.65000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26122538.52</v>
+        <v>14787261.75</v>
       </c>
       <c r="AK3" t="n">
-        <v>55904102.75</v>
+        <v>59320124.9</v>
       </c>
       <c r="AL3" t="n">
-        <v>8409648.109999999</v>
+        <v>-12325744.23</v>
       </c>
       <c r="AM3" t="n">
-        <v>-300138.84</v>
+        <v>12971.59</v>
       </c>
       <c r="AN3" t="n">
-        <v>-99972045.95999999</v>
+        <v>93129161.98</v>
       </c>
       <c r="AO3" t="n">
-        <v>68811108.88</v>
+        <v>43952975.65</v>
       </c>
       <c r="AP3" t="n">
-        <v>-104360930.19</v>
+        <v>-43115660.19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1537070475.94</v>
+        <v>-1212537850.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>-171898398.88</v>
+        <v>-190204476.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>-133308720.98</v>
+        <v>-121544157.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1231863356.08</v>
+        <v>-900789216.37</v>
       </c>
       <c r="AU3" t="n">
-        <v>1710242515.01</v>
+        <v>1299606486.04</v>
       </c>
       <c r="AV3" t="n">
-        <v>262753897.88</v>
+        <v>9093978.359999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>1447488617.13</v>
+        <v>1290512507.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-288128494.23</v>
+        <v>-252770688.25</v>
       </c>
       <c r="C4" t="n">
-        <v>-364000000</v>
+        <v>-691190000</v>
       </c>
       <c r="D4" t="n">
-        <v>643290000</v>
+        <v>922311050.89</v>
       </c>
       <c r="E4" t="n">
-        <v>-332081469.88</v>
+        <v>-321581797.13</v>
       </c>
       <c r="F4" t="n">
+        <v>86386632.39</v>
+      </c>
+      <c r="G4" t="n">
         <v>82767484.23999999</v>
       </c>
-      <c r="G4" t="n">
-        <v>46664971.38</v>
-      </c>
       <c r="H4" t="n">
-        <v>7405686.02</v>
+        <v>-1124576.23</v>
       </c>
       <c r="I4" t="n">
-        <v>28696826.84</v>
+        <v>4743724.38</v>
       </c>
       <c r="J4" t="n">
-        <v>311849952.66</v>
+        <v>256883711.93</v>
       </c>
       <c r="K4" t="n">
-        <v>51389981.98</v>
+        <v>62419264.24</v>
       </c>
       <c r="L4" t="n">
-        <v>-18830029.32</v>
+        <v>-36656603.2</v>
       </c>
       <c r="M4" t="n">
-        <v>279290000</v>
+        <v>231121050.89</v>
       </c>
       <c r="N4" t="n">
-        <v>279290000</v>
+        <v>231121050.89</v>
       </c>
       <c r="O4" t="n">
-        <v>-364000000</v>
+        <v>-691190000</v>
       </c>
       <c r="P4" t="n">
-        <v>643290000</v>
+        <v>922311050.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>-327106101.47</v>
+        <v>-320951096.43</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>4800528.41</v>
-      </c>
-      <c r="T4" t="n">
-        <v>37531656.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>-32731127.89</v>
+        <v>0</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>-331906629.88</v>
+        <v>-320951096.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>174840</v>
+        <v>630700.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>-332081469.88</v>
+        <v>-321581797.13</v>
       </c>
       <c r="AB4" t="n">
-        <v>43952975.65</v>
+        <v>68811108.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>-151505575.56</v>
+        <v>-21097165.89</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1029635.19</v>
+        <v>1494950.03</v>
       </c>
       <c r="AE4" t="n">
-        <v>287508151.73</v>
+        <v>1215391872.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>-115046910.3</v>
+        <v>-57629203.72</v>
       </c>
       <c r="AG4" t="n">
-        <v>-322937181.8</v>
+        <v>-1180354784.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>10967526.31</v>
+        <v>32787213.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>74107386.65000001</v>
+        <v>82026641.27</v>
       </c>
       <c r="AJ4" t="n">
-        <v>14787261.75</v>
+        <v>26122538.52</v>
       </c>
       <c r="AK4" t="n">
-        <v>59320124.9</v>
+        <v>55904102.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>-12325744.23</v>
+        <v>8409648.109999999</v>
       </c>
       <c r="AM4" t="n">
-        <v>12971.59</v>
+        <v>-300138.84</v>
       </c>
       <c r="AN4" t="n">
-        <v>93129161.98</v>
+        <v>-99972045.95999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>43952975.65</v>
+        <v>68811108.88</v>
       </c>
       <c r="AP4" t="n">
-        <v>-43115660.19</v>
+        <v>-104360930.19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1212537850.2</v>
+        <v>-1537070475.94</v>
       </c>
       <c r="AR4" t="n">
-        <v>-190204476.3</v>
+        <v>-171898398.88</v>
       </c>
       <c r="AS4" t="n">
-        <v>-121544157.53</v>
+        <v>-133308720.98</v>
       </c>
       <c r="AT4" t="n">
-        <v>-900789216.37</v>
+        <v>-1231863356.08</v>
       </c>
       <c r="AU4" t="n">
-        <v>1299606486.04</v>
+        <v>1710242515.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>9093978.359999999</v>
+        <v>262753897.88</v>
       </c>
       <c r="AW4" t="n">
-        <v>1290512507.68</v>
+        <v>1447488617.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>154209742.61</v>
+        <v>641226060.6900001</v>
       </c>
       <c r="C5" t="n">
-        <v>-1063500000</v>
+        <v>-822120287</v>
       </c>
       <c r="D5" t="n">
-        <v>688700000</v>
+        <v>562863380</v>
       </c>
       <c r="E5" t="n">
-        <v>-41878422.92</v>
+        <v>-77031590.34999999</v>
       </c>
       <c r="F5" t="n">
-        <v>46664971.38</v>
+        <v>317660382.5</v>
       </c>
       <c r="G5" t="n">
-        <v>15726821.66</v>
+        <v>86386632.39</v>
       </c>
       <c r="H5" t="n">
-        <v>-1238357.62</v>
+        <v>-16463297.78</v>
       </c>
       <c r="I5" t="n">
-        <v>32176507.34</v>
+        <v>247737047.89</v>
       </c>
       <c r="J5" t="n">
-        <v>-205532468.87</v>
+        <v>-327557100.29</v>
       </c>
       <c r="K5" t="n">
-        <v>206848312.56</v>
+        <v>-45977060.23</v>
       </c>
       <c r="L5" t="n">
-        <v>-37580781.43</v>
+        <v>-22323133.06</v>
       </c>
       <c r="M5" t="n">
-        <v>-374800000</v>
+        <v>-259256907</v>
       </c>
       <c r="N5" t="n">
-        <v>-374800000</v>
+        <v>-259256907</v>
       </c>
       <c r="O5" t="n">
-        <v>-1063500000</v>
+        <v>-822120287</v>
       </c>
       <c r="P5" t="n">
-        <v>688700000</v>
+        <v>562863380</v>
       </c>
       <c r="Q5" t="n">
-        <v>41620810.68</v>
+        <v>-142963502.86</v>
       </c>
       <c r="R5" t="n">
-        <v>-41878422.92</v>
-      </c>
-      <c r="S5" t="n">
-        <v>19684120.86</v>
-      </c>
-      <c r="T5" t="n">
-        <v>19684120.86</v>
-      </c>
+        <v>-114375086.02</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>63610580.74</v>
+        <v>47574487.21</v>
       </c>
       <c r="W5" t="n">
-        <v>163589450.19</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-99978869.45</v>
-      </c>
+        <v>47574487.21</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>-41673890.92</v>
+        <v>-76162904.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>204532</v>
+        <v>868686.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>-41878422.92</v>
+        <v>-77031590.34999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>196088165.53</v>
+        <v>718257651.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>-37883747.65</v>
+        <v>717626647.8200001</v>
       </c>
       <c r="AD5" t="n">
-        <v>2433393.19</v>
+        <v>-25911.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>-47233725.54</v>
+        <v>1372153016.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>-81655766.59999999</v>
+        <v>-205052323.32</v>
       </c>
       <c r="AG5" t="n">
-        <v>88572351.3</v>
+        <v>-449448134.66</v>
       </c>
       <c r="AH5" t="n">
-        <v>26912309.32</v>
+        <v>26979042.49</v>
       </c>
       <c r="AI5" t="n">
-        <v>78897030.84999999</v>
+        <v>96135077.93000001</v>
       </c>
       <c r="AJ5" t="n">
-        <v>13024098.24</v>
+        <v>25263435.84</v>
       </c>
       <c r="AK5" t="n">
-        <v>65872932.61</v>
+        <v>70871642.09</v>
       </c>
       <c r="AL5" t="n">
-        <v>-55763281.11</v>
+        <v>-275560716.9</v>
       </c>
       <c r="AM5" t="n">
-        <v>-249860.08</v>
+        <v>755440.42</v>
       </c>
       <c r="AN5" t="n">
-        <v>150414402.81</v>
+        <v>147106347.41</v>
       </c>
       <c r="AO5" t="n">
-        <v>196088165.53</v>
+        <v>718257651.04</v>
       </c>
       <c r="AP5" t="n">
-        <v>-53287273.97</v>
+        <v>-48375280.36</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-821986198.3099999</v>
+        <v>-726616683.37</v>
       </c>
       <c r="AR5" t="n">
-        <v>-102160445.75</v>
+        <v>-191509100.43</v>
       </c>
       <c r="AS5" t="n">
-        <v>-107244792.38</v>
+        <v>-168741766.27</v>
       </c>
       <c r="AT5" t="n">
-        <v>-612580960.1799999</v>
+        <v>-366365816.67</v>
       </c>
       <c r="AU5" t="n">
-        <v>1071361637.81</v>
+        <v>1493249614.77</v>
       </c>
       <c r="AV5" t="n">
-        <v>104195013.18</v>
+        <v>149997154.96</v>
       </c>
       <c r="AW5" t="n">
-        <v>967166624.63</v>
+        <v>1343252459.81</v>
       </c>
     </row>
   </sheetData>
@@ -3958,197 +3958,197 @@
       </c>
       <c r="DF1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
         <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="ES1" t="inlineStr">
@@ -4253,28 +4253,28 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>13.75</v>
+        <v>16.13</v>
       </c>
       <c r="V2" t="n">
-        <v>12.01</v>
+        <v>16.13</v>
       </c>
       <c r="W2" t="n">
-        <v>13.31</v>
+        <v>16.13</v>
       </c>
       <c r="X2" t="n">
-        <v>14.48</v>
+        <v>16.13</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.75</v>
+        <v>16.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.01</v>
+        <v>16.13</v>
       </c>
       <c r="AA2" t="n">
-        <v>13.31</v>
+        <v>16.13</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.48</v>
+        <v>16.13</v>
       </c>
       <c r="AC2" t="n">
         <v>1338854400</v>
@@ -4283,34 +4283,34 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.46</v>
+        <v>0.437</v>
       </c>
       <c r="AF2" t="n">
-        <v>191.42856</v>
+        <v>253.42857</v>
       </c>
       <c r="AG2" t="n">
-        <v>53.6</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="AH2" t="n">
-        <v>78815146</v>
+        <v>5813405</v>
       </c>
       <c r="AI2" t="n">
-        <v>78815146</v>
+        <v>5813405</v>
       </c>
       <c r="AJ2" t="n">
-        <v>38992340</v>
+        <v>40667482</v>
       </c>
       <c r="AK2" t="n">
-        <v>45273783</v>
+        <v>80372054</v>
       </c>
       <c r="AL2" t="n">
-        <v>45273783</v>
+        <v>80372054</v>
       </c>
       <c r="AM2" t="n">
-        <v>13.37</v>
+        <v>16.13</v>
       </c>
       <c r="AN2" t="n">
-        <v>13.38</v>
+        <v>14.67</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -4319,13 +4319,13 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10380621824</v>
+        <v>13742703616</v>
       </c>
       <c r="AR2" t="n">
-        <v>10380622220</v>
+        <v>12495480329</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.970000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="AT2" t="n">
         <v>16.6</v>
@@ -4337,13 +4337,13 @@
         <v>1.076923</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.224574</v>
+        <v>10.888353</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.7304</v>
+        <v>13.2868</v>
       </c>
       <c r="AY2" t="n">
-        <v>13.2782</v>
+        <v>13.2828</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>10284424192</v>
+        <v>13646505984</v>
       </c>
       <c r="BE2" t="n">
         <v>0.042930003</v>
@@ -4375,7 +4375,7 @@
         <v>0.30723</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0145000005</v>
+        <v>0.01446</v>
       </c>
       <c r="BJ2" t="n">
         <v>774673300</v>
@@ -4384,7 +4384,7 @@
         <v>2.297</v>
       </c>
       <c r="BL2" t="n">
-        <v>5.8336964</v>
+        <v>7.7231174</v>
       </c>
       <c r="BM2" t="n">
         <v>1767139200</v>
@@ -4416,16 +4416,16 @@
         <v>1435104000</v>
       </c>
       <c r="BV2" t="n">
-        <v>8.148</v>
+        <v>10.812</v>
       </c>
       <c r="BW2" t="n">
-        <v>83.254</v>
+        <v>110.471</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.47577095</v>
+        <v>0.67671514</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.033333</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="CC2" t="n">
-        <v>13.4</v>
+        <v>17.74</v>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
@@ -4543,148 +4543,148 @@
       </c>
       <c r="DF2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>1782111876</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>finmb_22534323</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>9.981405000000001</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
           <t>GUANGDONG ORIENT ZIRCONIC IND S</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
         <is>
           <t>Guangdong Orient Zirconic Ind Sci &amp; Tech Co.,Ltd</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DI2" t="b">
+      <c r="DS2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>4.4531994</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.33515966</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>4.4572</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.33556178</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>Guangdong Orient Zirconic Ind Sci &amp; Tech Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EB2" t="b">
         <v>0</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="EC2" t="n">
+        <v>1618657140</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>1618657140</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="EF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
         <v>1189647000000</v>
       </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>1780038300</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>finmb_22534323</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>Guangdong Orient Zirconic Ind Sci &amp; Tech Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.35000038</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>13.31 - 14.48</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="EH2" t="n">
+        <v>1.6100006</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>16.13 - 16.13</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="EA2" t="n">
-        <v>38992340</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>4.4299994</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.49386835</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>8.97 - 16.6</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>-3.2000008</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.19277112</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>47.577095</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1618657140</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1618657140</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="EK2" t="n">
-        <v>0.25</v>
+        <v>40667482</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.6695995300000001</v>
+        <v>8.51</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.05259847</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>0.12179947</v>
+        <v>0.9219935500000001</v>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>9.23 - 16.6</t>
+        </is>
       </c>
       <c r="EO2" t="n">
-        <v>0.00917289</v>
+        <v>1.1399994</v>
       </c>
       <c r="EP2" t="n">
-        <v>15</v>
+        <v>0.06867466</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-2.5454574</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>13.4</v>
+        <v>67.67152</v>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
       </c>
       <c r="ES2" t="inlineStr"/>
     </row>
